--- a/artfynd/A 947-2025 artfynd.xlsx
+++ b/artfynd/A 947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133874965</v>
       </c>
       <c r="B2" t="n">
-        <v>106174</v>
+        <v>106178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 947-2025 artfynd.xlsx
+++ b/artfynd/A 947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133874965</v>
       </c>
       <c r="B2" t="n">
-        <v>106178</v>
+        <v>106180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 947-2025 artfynd.xlsx
+++ b/artfynd/A 947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133874965</v>
       </c>
       <c r="B2" t="n">
-        <v>106222</v>
+        <v>106229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 947-2025 artfynd.xlsx
+++ b/artfynd/A 947-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>133874965</v>
       </c>
       <c r="B2" t="n">
-        <v>106229</v>
+        <v>106236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,6 +774,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133875028</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skjutbanan S Sofielund Arboga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>550081</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6583711</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 947-2025 artfynd.xlsx
+++ b/artfynd/A 947-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133874965</v>
+        <v>134812574</v>
       </c>
       <c r="B2" t="n">
-        <v>106236</v>
+        <v>107420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>942</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Hjärtstilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Leonurus cardiaca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -704,24 +704,27 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skjutbanan S Sofielund Arboga, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550151</v>
+        <v>550174</v>
       </c>
       <c r="R2" t="n">
-        <v>6583705</v>
+        <v>6583713</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133875028</v>
+        <v>133874965</v>
       </c>
       <c r="B3" t="n">
-        <v>103907</v>
+        <v>106236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223284</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -806,16 +810,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skjutbanan S Sofielund Arboga, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550081</v>
+        <v>550151</v>
       </c>
       <c r="R3" t="n">
-        <v>6583711</v>
+        <v>6583705</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -871,6 +880,598 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134812621</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skjutbanan S Sofielund Arboga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6583720</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134812602</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107695</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221705</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängskovall</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skjutbanan S Sofielund Arboga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6583716</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134812684</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skjutbanan S Sofielund Arboga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>550135</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6583682</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134812657</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skjutbanan S Sofielund Arboga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550141</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6583716</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134812695</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skjutbanan S Sofielund Arboga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6583720</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133875028</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skjutbanan S Sofielund Arboga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>550081</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6583711</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 947-2025 artfynd.xlsx
+++ b/artfynd/A 947-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134812574</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133874965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134812621</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134812602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134812684</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134812657</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134812695</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,8 +1512,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133875028</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>